--- a/元ファイルとの照合結果.xlsx
+++ b/元ファイルとの照合結果.xlsx
@@ -521,7 +521,7 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>退職等_預金・立替・未収</t>
+          <t>退職等_預金・立替・未収P36</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
@@ -562,7 +562,7 @@
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>退職等_預金・立替・未収</t>
+          <t>退職等_預金・立替・未収P36</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
@@ -603,7 +603,7 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>保健_附属明細表</t>
+          <t>保健_附属明細表P54-57</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
@@ -644,7 +644,7 @@
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>保健_附属明細表</t>
+          <t>保健_附属明細表P54-57</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
@@ -685,7 +685,7 @@
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>保健_附属明細表</t>
+          <t>保健_附属明細表P54-57</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
@@ -726,7 +726,7 @@
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>保健_附属明細表</t>
+          <t>保健_附属明細表P54-57</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
@@ -767,7 +767,7 @@
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>貸付_財務諸表</t>
+          <t>貸付_財務諸表P59</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
@@ -808,7 +808,7 @@
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>貸付_財務諸表</t>
+          <t>貸付_財務諸表P59</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
@@ -1054,7 +1054,7 @@
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>短期_附属明細表</t>
+          <t>短期_附属明細表P28-29</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
@@ -1099,7 +1099,7 @@
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>短期_決算精算表</t>
+          <t>短期_決算精算表P30</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
@@ -1144,7 +1144,7 @@
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>厚生_決算精算表</t>
+          <t>厚生_決算精算表P33</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr">
@@ -1634,7 +1634,7 @@
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>短期_財務諸表</t>
+          <t>短期_財務諸表P27</t>
         </is>
       </c>
       <c r="B20" s="2" t="n">
@@ -1651,7 +1651,7 @@
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>短期_附属明細表</t>
+          <t>短期_附属明細表P28-29</t>
         </is>
       </c>
       <c r="B21" s="2" t="n">
@@ -1668,7 +1668,7 @@
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>短期_決算精算表</t>
+          <t>短期_決算精算表P30</t>
         </is>
       </c>
       <c r="B22" s="2" t="n">
@@ -1685,7 +1685,7 @@
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>厚生_貸借・損益</t>
+          <t>厚生_貸借・損益P31</t>
         </is>
       </c>
       <c r="B23" s="2" t="n">
@@ -1702,7 +1702,7 @@
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>厚生_預金・立替・未収</t>
+          <t>厚生_預金・立替・未収P32</t>
         </is>
       </c>
       <c r="B24" s="2" t="n">
@@ -1719,7 +1719,7 @@
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>厚生_決算精算表</t>
+          <t>厚生_決算精算表P33</t>
         </is>
       </c>
       <c r="B25" s="2" t="n">
@@ -1736,7 +1736,7 @@
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>厚生_白紙</t>
+          <t>厚生_白紙P34</t>
         </is>
       </c>
       <c r="B26" s="2" t="n">
@@ -1757,7 +1757,7 @@
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>退職等_貸借・損益</t>
+          <t>退職等_貸借・損益P35</t>
         </is>
       </c>
       <c r="B27" s="2" t="n">
@@ -1774,7 +1774,7 @@
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>退職等_預金・立替・未収</t>
+          <t>退職等_預金・立替・未収P36</t>
         </is>
       </c>
       <c r="B28" s="2" t="n">
@@ -1791,7 +1791,7 @@
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>退職等_決算精算表</t>
+          <t>退職等_決算精算表P37</t>
         </is>
       </c>
       <c r="B29" s="2" t="n">
@@ -1808,7 +1808,7 @@
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>退職等_白紙</t>
+          <t>退職等_白紙P38</t>
         </is>
       </c>
       <c r="B30" s="2" t="n">
@@ -1829,7 +1829,7 @@
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>経過的_貸借・損益</t>
+          <t>経過的_貸借・損益P39</t>
         </is>
       </c>
       <c r="B31" s="2" t="n">
@@ -1846,7 +1846,7 @@
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>経過的_預金・立替・未収</t>
+          <t>経過的_預金・立替・未収P40</t>
         </is>
       </c>
       <c r="B32" s="2" t="n">
@@ -1863,7 +1863,7 @@
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>経過的_決算精算表</t>
+          <t>経過的_決算精算表P41</t>
         </is>
       </c>
       <c r="B33" s="2" t="n">
@@ -1880,7 +1880,7 @@
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>経過的_白紙</t>
+          <t>経過的_白紙P42</t>
         </is>
       </c>
       <c r="B34" s="2" t="n">
@@ -1901,7 +1901,7 @@
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>預託金_貸借・損益</t>
+          <t>預託金_貸借・損益P43</t>
         </is>
       </c>
       <c r="B35" s="2" t="n">
@@ -1918,7 +1918,7 @@
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>預託金_預金・未収・貸付・預託金</t>
+          <t>預託金_預金・未収・貸付・預託金P44</t>
         </is>
       </c>
       <c r="B36" s="2" t="n">
@@ -1935,7 +1935,7 @@
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
-          <t>預託金_決算精算表</t>
+          <t>預託金_決算精算表P45</t>
         </is>
       </c>
       <c r="B37" s="2" t="n">
@@ -1952,7 +1952,7 @@
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>預託金_白紙</t>
+          <t>預託金_白紙P46</t>
         </is>
       </c>
       <c r="B38" s="2" t="n">
@@ -1973,7 +1973,7 @@
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t>業務_財務諸表</t>
+          <t>業務_財務諸表P47</t>
         </is>
       </c>
       <c r="B39" s="2" t="n">
@@ -1990,7 +1990,7 @@
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>業務_附属明細表</t>
+          <t>業務_附属明細表P48-50</t>
         </is>
       </c>
       <c r="B40" s="2" t="n">
@@ -2007,7 +2007,7 @@
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
-          <t>業務_決算精算表</t>
+          <t>業務_決算精算表P51</t>
         </is>
       </c>
       <c r="B41" s="2" t="n">
@@ -2024,7 +2024,7 @@
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>業務_白紙</t>
+          <t>業務_白紙P52</t>
         </is>
       </c>
       <c r="B42" s="2" t="n">
@@ -2045,7 +2045,7 @@
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
         <is>
-          <t>保健_財務諸表</t>
+          <t>保健_財務諸表P53</t>
         </is>
       </c>
       <c r="B43" s="2" t="n">
@@ -2062,7 +2062,7 @@
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>保健_附属明細表</t>
+          <t>保健_附属明細表P54-57</t>
         </is>
       </c>
       <c r="B44" s="2" t="n">
@@ -2079,7 +2079,7 @@
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
         <is>
-          <t>保健_決算精算表</t>
+          <t>保健_決算精算表P58</t>
         </is>
       </c>
       <c r="B45" s="2" t="n">
@@ -2096,7 +2096,7 @@
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>貸付_財務諸表</t>
+          <t>貸付_財務諸表P59</t>
         </is>
       </c>
       <c r="B46" s="2" t="n">
@@ -2113,7 +2113,7 @@
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
         <is>
-          <t>貸付_附属明細表</t>
+          <t>貸付_附属明細表P60-62</t>
         </is>
       </c>
       <c r="B47" s="2" t="n">
@@ -2130,7 +2130,7 @@
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>貸付_決算精算表</t>
+          <t>貸付_決算精算表P63</t>
         </is>
       </c>
       <c r="B48" s="2" t="n">
@@ -2147,7 +2147,7 @@
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
         <is>
-          <t>貸付_白紙</t>
+          <t>貸付_白紙P64</t>
         </is>
       </c>
       <c r="B49" s="2" t="n">

--- a/元ファイルとの照合結果.xlsx
+++ b/元ファイルとの照合結果.xlsx
@@ -454,7 +454,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I19"/>
+  <dimension ref="A1:I17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -767,24 +767,24 @@
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>貸付_財務諸表P59</t>
+          <t>報告_短期P11-13</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>F20</t>
+          <t>AD18</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>欠損金補てん積立金</t>
+          <t>家族・移送費 前年度1件当たり金額（移送費）</t>
         </is>
       </c>
       <c r="E8" s="3" t="n">
-        <v>1966406293</v>
+        <v>0</v>
       </c>
       <c r="F8" s="3" t="n">
-        <v>1957132740</v>
+        <v>70824</v>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
@@ -793,7 +793,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>統合後は積立金明細表の計上額を参照。純資産合計(H23)は同額。</t>
+          <t>元は0の固定値。同じ表の元データ（HT20=70,824、GD20=1件）から算出すると70,824。</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -808,24 +808,24 @@
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>貸付_財務諸表P59</t>
+          <t>報告_短期P11-13</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>F22</t>
+          <t>AA49</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>積立金（下段）</t>
+          <t>本人・訪問看護 前年度対比（件数）</t>
         </is>
       </c>
       <c r="E9" s="3" t="n">
-        <v>-9273553</v>
+        <v>0</v>
       </c>
       <c r="F9" s="3" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
@@ -834,7 +834,7 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>F20との振り替わり。F20+F22の合計は同額。</t>
+          <t>元は0の固定値。他の行と同じ算出式に変更。</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
@@ -854,19 +854,19 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>AD18</t>
+          <t>AP49</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>家族・移送費 前年度1件当たり金額（移送費）</t>
+          <t>同（日数）</t>
         </is>
       </c>
       <c r="E10" s="3" t="n">
         <v>0</v>
       </c>
       <c r="F10" s="3" t="n">
-        <v>70824</v>
+        <v>85.70999999999999</v>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
@@ -875,7 +875,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>元は0の固定値。同じ表の元データ（HT20=70,824、GD20=1件）から算出すると70,824。</t>
+          <t>同上。</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -890,24 +890,24 @@
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>報告_短期P11-13</t>
+          <t>報告_P8グラフデータ</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>AA49</t>
+          <t>B8</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>本人・訪問看護 前年度対比（件数）</t>
+          <t>交付金（1人当たり金額）</t>
         </is>
       </c>
       <c r="E11" s="3" t="n">
-        <v>0</v>
+        <v>36502</v>
       </c>
       <c r="F11" s="3" t="n">
-        <v>100</v>
+        <v>36503</v>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
@@ -916,12 +916,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>元は0の固定値。他の行と同じ算出式に変更。</t>
+          <t>元は手補正。G8=36,502.9を四捨五入すると36,503。元のP8吹き出し図形も36,503。</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>要確認</t>
+          <t>統合後が妥当</t>
         </is>
       </c>
     </row>
@@ -931,24 +931,24 @@
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>報告_短期P11-13</t>
+          <t>報告_P8グラフデータ</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>AP49</t>
+          <t>B11</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>同（日数）</t>
+          <t>収入 合計</t>
         </is>
       </c>
       <c r="E12" s="3" t="n">
-        <v>0</v>
+        <v>674925</v>
       </c>
       <c r="F12" s="3" t="n">
-        <v>85.70999999999999</v>
+        <v>674926</v>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
@@ -957,12 +957,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>同上。</t>
+          <t>B8の+1による。</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>要確認</t>
+          <t>統合後が妥当</t>
         </is>
       </c>
     </row>
@@ -972,38 +972,42 @@
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>報告_P8グラフデータ</t>
+          <t>短期_附属明細表P28-29</t>
         </is>
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>B8</t>
+          <t>E110</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>交付金（1人当たり金額）</t>
-        </is>
-      </c>
-      <c r="E13" s="3" t="n">
-        <v>36502</v>
-      </c>
-      <c r="F13" s="3" t="n">
-        <v>36503</v>
+          <t>利益剰余金計算書の見出し</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>介護欠損金</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>介護積立金</t>
+        </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>数値</t>
+          <t>文字</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>元は手補正。G8=36,502.9を四捨五入すると36,503。元のP8吹き出し図形も36,503。</t>
+          <t>金額が+111,039,759円（プラス）のため見出しを自動切替。</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>統合後が妥当</t>
+          <t>要確認</t>
         </is>
       </c>
     </row>
@@ -1013,33 +1017,37 @@
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>報告_P8グラフデータ</t>
+          <t>短期_決算精算表P30</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>B11</t>
+          <t>I48</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>収入 合計</t>
-        </is>
-      </c>
-      <c r="E14" s="3" t="n">
-        <v>674925</v>
-      </c>
-      <c r="F14" s="3" t="n">
-        <v>674926</v>
+          <t>●6年度決算上の次年度繰越支払準備金</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>●6年度…</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>●7年度…</t>
+        </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>数値</t>
+          <t>文字</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>B8の+1による。</t>
+          <t>年度表記を入力ガイドC6に連動。</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1054,27 +1062,27 @@
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>短期_附属明細表P28-29</t>
+          <t>厚生_決算精算表P33</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>E110</t>
+          <t>A25</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>利益剰余金計算書の見出し</t>
+          <t>作成日（令和 8年 4月22日）</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>介護欠損金</t>
+          <t>令和　8年（半角8）</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>介護積立金</t>
+          <t>令和　８年（全角８）</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -1084,12 +1092,12 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>金額が+111,039,759円（プラス）のため見出しを自動切替。</t>
+          <t>数式で作成した日付。数字の全角・半角のみ。</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>要確認</t>
+          <t>表記のみ</t>
         </is>
       </c>
     </row>
@@ -1099,42 +1107,42 @@
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>短期_決算精算表P30</t>
+          <t>報告_短期P6</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>I48</t>
+          <t>I19</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>●6年度決算上の次年度繰越支払準備金</t>
+          <t>結合セル(B19:N19)内の非表示テキスト</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>●6年度…</t>
+          <t>一 般 職</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>●7年度…</t>
+          <t>（空）</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>文字</t>
+          <t>参考</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>年度表記を入力ガイドC6に連動。</t>
+          <t>結合セルの左上(B19)は一致。表示される内容に差なし。</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>統合後が妥当</t>
+          <t>差なし</t>
         </is>
       </c>
     </row>
@@ -1144,130 +1152,40 @@
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>厚生_決算精算表P33</t>
+          <t>報告_短期P11-13</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>A25</t>
+          <t>I59</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>作成日（令和 8年 4月22日）</t>
+          <t>結合セル(D59:O59)内の非表示テキスト</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>令和　8年（半角8）</t>
+          <t>計</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>令和　８年（全角８）</t>
+          <t>（空）</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>文字</t>
+          <t>参考</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>数式で作成した日付。数字の全角・半角のみ。</t>
+          <t>同上。</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>表記のみ</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="2" t="n">
-        <v>17</v>
-      </c>
-      <c r="B18" s="2" t="inlineStr">
-        <is>
-          <t>報告_短期P6</t>
-        </is>
-      </c>
-      <c r="C18" s="2" t="inlineStr">
-        <is>
-          <t>I19</t>
-        </is>
-      </c>
-      <c r="D18" s="2" t="inlineStr">
-        <is>
-          <t>結合セル(B19:N19)内の非表示テキスト</t>
-        </is>
-      </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>一 般 職</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>（空）</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>参考</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>結合セルの左上(B19)は一致。表示される内容に差なし。</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>差なし</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="2" t="n">
-        <v>18</v>
-      </c>
-      <c r="B19" s="2" t="inlineStr">
-        <is>
-          <t>報告_短期P11-13</t>
-        </is>
-      </c>
-      <c r="C19" s="2" t="inlineStr">
-        <is>
-          <t>I59</t>
-        </is>
-      </c>
-      <c r="D19" s="2" t="inlineStr">
-        <is>
-          <t>結合セル(D59:O59)内の非表示テキスト</t>
-        </is>
-      </c>
-      <c r="E19" s="2" t="inlineStr">
-        <is>
-          <t>計</t>
-        </is>
-      </c>
-      <c r="F19" s="2" t="inlineStr">
-        <is>
-          <t>（空）</t>
-        </is>
-      </c>
-      <c r="G19" s="2" t="inlineStr">
-        <is>
-          <t>参考</t>
-        </is>
-      </c>
-      <c r="H19" s="2" t="inlineStr">
-        <is>
-          <t>同上。</t>
-        </is>
-      </c>
-      <c r="I19" s="2" t="inlineStr">
         <is>
           <t>差なし</t>
         </is>
@@ -2103,10 +2021,10 @@
         <v>131</v>
       </c>
       <c r="C46" s="2" t="n">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="D46" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E46" s="2" t="inlineStr"/>
     </row>
@@ -2175,10 +2093,10 @@
         <v>7677</v>
       </c>
       <c r="C50" s="2" t="n">
-        <v>7659</v>
+        <v>7661</v>
       </c>
       <c r="D50" s="2" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="E50" s="2" t="inlineStr"/>
     </row>
@@ -2256,7 +2174,7 @@
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>今回の修正（配色・文言・マクロ・黄色表示）では、帳票シートの値・数式を変更していない。上の相違は、統合ブックの作成時点で生じたもの。</t>
+          <t>今回の修正（配色・文言・マクロ・黄色表示）では、帳票シートの値・数式を変更していない。上の相違は、統合ブックの作成時点で生じたもの。 貸付_財務諸表の欠損金補てん積立金（F20・F22）は、元ファイルを正として元の値に戻したため、相違から除いた。</t>
         </is>
       </c>
     </row>
